--- a/reports/jobs_2026-10-09.xlsx
+++ b/reports/jobs_2026-10-09.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Intern- Employee Engagement</t>
+          <t>Global Data Sharing Engineer United States - Texas - Austin Technology</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+          <t>https://careers.expediagroup.com/job/global-data-sharing-engineer/austin-tx/R-110073-1/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -561,57 +561,57 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Fractal Analytics</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>AI / ML</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://fractal.ai/careers/</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 0 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -624,11 +624,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -636,12 +632,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -658,7 +654,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Chiang Mai 0 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -683,7 +679,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -705,7 +701,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -730,7 +726,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -777,7 +773,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -799,7 +795,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -812,7 +808,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -820,7 +820,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
+          <t>Key Takeaways from Agoda’s AI Developer Report 2026 September 29, 2026 /</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-agodas-ai-developer-report-2026/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>How Agoda is evolving engineering support with AI agents September 22, 2026 /</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -941,11 +941,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -953,7 +949,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/blog/tech/how-agoda-is-evolving-engineering-support-with-ai-agents/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -975,12 +971,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -988,7 +984,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -996,7 +996,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Graphics Engineer</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/cambridge/graphics-engineer/33099/96521990288</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Graphics Engineer</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://careers.arm.com/job/cambridge/graphics-engineer/33099/96521990288</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1185,12 +1185,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Theorem Proving Engineer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1357,17 +1357,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1375,11 +1375,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Electronic City,  Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -1387,12 +1383,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000154002299</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1404,17 +1400,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Electronic City,  Bengaluru, in</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1434,12 +1430,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000154002299</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1456,12 +1452,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1471,7 +1467,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1481,7 +1477,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1503,12 +1499,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1518,7 +1514,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1528,7 +1524,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1550,7 +1546,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1565,7 +1561,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1575,7 +1571,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1597,12 +1593,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1610,7 +1606,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1653,11 +1653,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -1665,7 +1661,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1687,7 +1683,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1712,7 +1708,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1734,7 +1730,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1759,7 +1755,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1781,7 +1777,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1806,7 +1802,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1828,12 +1824,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1853,7 +1849,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1875,12 +1871,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1900,7 +1896,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1922,12 +1918,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1947,7 +1943,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1964,17 +1960,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1984,7 +1980,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1994,12 +1990,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2011,12 +2007,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Expedia Group India</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CA Industrial Trainee</t>
+          <t>Global Data Sharing Engineer United States - Washington - Seattle Technology</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2037,12 +2033,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Mumbai/CA-Industrial-Trainee_SR-46509-1</t>
+          <t>https://careers.expediagroup.com/job/global-data-sharing-engineer/seattle-wa/R-110073/</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://careers.expediagroup.com/jobs/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2054,17 +2050,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2072,7 +2068,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>AI Governance Arcitect</t>
+          <t>CA Industrial Trainee</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/CA-Industrial-Trainee_SR-46509-1</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/MLOps-Engineer_SR-46499-1</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>AI Governance Arcitect</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2226,17 +2226,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/Data-Engineer_SR-46461-1</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2269,17 +2269,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2312,12 +2312,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2373,11 +2373,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2385,12 +2381,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2402,17 +2398,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2420,11 +2416,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2432,12 +2424,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2449,17 +2441,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2469,7 +2461,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2479,12 +2471,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2496,17 +2488,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2516,7 +2508,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2526,12 +2518,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2543,17 +2535,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2563,7 +2555,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2573,12 +2565,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2590,17 +2582,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2608,7 +2600,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2616,12 +2612,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2633,17 +2629,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2651,7 +2647,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2676,17 +2676,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2694,11 +2694,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2706,12 +2702,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2723,12 +2719,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2741,11 +2737,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2753,12 +2745,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2770,12 +2762,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2788,7 +2780,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -2796,12 +2792,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2813,12 +2809,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2833,7 +2829,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2843,12 +2839,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2860,17 +2856,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2886,12 +2882,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2903,17 +2899,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2923,7 +2919,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2933,12 +2929,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2950,17 +2946,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2976,12 +2972,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -2993,17 +2989,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3013,7 +3009,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3023,12 +3019,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://www.okta.com/company/careers/opportunity/8243101?gh_jid=8243101</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3040,12 +3036,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3058,11 +3054,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -3070,12 +3062,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3092,7 +3084,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3107,7 +3099,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3117,7 +3109,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3139,7 +3131,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3164,7 +3156,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3186,7 +3178,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3211,7 +3203,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3228,17 +3220,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3246,7 +3238,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -3254,12 +3250,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3271,17 +3267,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3291,7 +3287,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3301,12 +3297,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3318,12 +3314,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3336,11 +3332,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -3348,12 +3340,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3370,7 +3362,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3395,7 +3387,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3412,17 +3404,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3430,7 +3422,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -3438,12 +3434,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3455,17 +3451,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3475,7 +3471,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3485,12 +3481,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3502,12 +3498,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3520,11 +3516,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -3532,12 +3524,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3549,12 +3541,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3569,7 +3561,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3579,12 +3571,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4739199005</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3601,22 +3593,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3626,7 +3618,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3648,12 +3640,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3663,7 +3655,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3673,7 +3665,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3695,7 +3687,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3705,12 +3697,12 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3720,7 +3712,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -3742,22 +3734,22 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer- SaaS O365</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3767,7 +3759,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -3789,12 +3781,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3804,7 +3796,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3814,7 +3806,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -3831,27 +3823,27 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Software Engineer- SaaS O365</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3861,12 +3853,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3878,17 +3870,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3896,7 +3888,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -3904,12 +3900,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3921,17 +3917,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3939,7 +3935,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -3947,12 +3947,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4050,17 +4050,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4068,11 +4068,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -4080,12 +4076,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4097,17 +4093,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4115,11 +4111,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
       <c r="F81" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -4127,12 +4119,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4144,17 +4136,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4162,7 +4154,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -4170,12 +4166,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4187,17 +4183,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4207,7 +4203,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4217,12 +4213,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4234,12 +4230,12 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Developer (Vapasi) - Intern</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4249,14 +4245,10 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>1–5 years</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -4264,12 +4256,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4281,12 +4273,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Software Procurement Intern</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4299,11 +4291,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Gurgaon, India; Pune, India</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
@@ -4311,12 +4299,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4328,17 +4316,17 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4348,7 +4336,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4358,12 +4346,12 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -4375,52 +4363,193 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Developer (Vapasi) - Intern</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>1–5 years</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, India</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Software Procurement Intern</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Gurgaon, India; Pune, India</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
           <t>Unacademy</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr">
+      <c r="I90" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I87"/>
+  <autoFilter ref="A1:I90"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4508,6 +4637,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4519,7 +4651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4607,35 +4739,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kiwi</t>
+          <t>Signzy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.gokiwi.in/careers</t>
+          <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.gokiwi.in/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Signzy</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.signzy.com/careers/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4644,18 +4756,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4664,18 +4776,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4684,18 +4796,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4704,18 +4816,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4724,6 +4836,26 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Darwinbox</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://darwinbox.com/careers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -4787,19 +4919,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FirstCry</t>
+          <t>PharmEasy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.firstcry.com/careers</t>
+          <t>https://pharmeasy.in/careers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+  - navigating to "https://pharmeasy.in/careers", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -4827,15 +4959,115 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Swiggy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://careers.swiggy.com/</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://careers.swiggy.com/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coforge</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.coforge.com/careers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
+Call log:
+  - navigating to "https://www.coforge.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.persistent.com/careers/</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
+Call log:
+  - navigating to "https://www.persistent.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Udaan</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://udaan.com/careers</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://udaan.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Zoom India</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://careers.zoom.us/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_CONNECTION_RESET at https://careers.zoom.us/
 Call log:
@@ -4844,86 +5076,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Coforge</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://www.coforge.com/careers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
-Call log:
-  - navigating to "https://www.coforge.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Swiggy</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://careers.swiggy.com/</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://careers.swiggy.com/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Persistent Systems</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://www.persistent.com/careers/</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
-Call log:
-  - navigating to "https://www.persistent.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Udaan</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://udaan.com/careers</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://udaan.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
